--- a/pecas_consolidadas.xlsx
+++ b/pecas_consolidadas.xlsx
@@ -796,7 +796,7 @@
         <v>BR200155</v>
       </c>
       <c r="B50" t="str">
-        <v>Motopolia 80S AC 0,085KW 2P 0,22M/S 60HZ 1X230V MO</v>
+        <v>Motopolia 80S AC 0,085KW 2P 0,22M/S 60HZ 1X230V MO para CX5030T</v>
       </c>
     </row>
     <row r="51">
